--- a/Bauteile/Zahlungen.xlsx
+++ b/Bauteile/Zahlungen.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\Reaction-game\Bauteile\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\private\reaction-game\Bauteile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC939DC1-F3E3-47D5-9829-627814D94F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4893A0D3-3C8B-40BA-A4D3-3CA66CA12C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Lieferant</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Rest</t>
+  </si>
+  <si>
+    <t>AEK Karte Simon</t>
   </si>
 </sst>
 </file>
@@ -410,15 +413,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.07421875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.86328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.19921875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.3828125" customWidth="1"/>
+    <col min="3" max="3" width="12.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -429,7 +432,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -440,7 +443,7 @@
         <v>706.33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
@@ -451,7 +454,7 @@
         <v>139.6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
         <v>5</v>
       </c>
@@ -462,7 +465,7 @@
         <v>38.85</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
@@ -473,30 +476,41 @@
         <v>105.63</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B7" s="2" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="4">
+        <v>64.900000000000006</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="1">
-        <f>SUM(C2:C5)</f>
-        <v>990.41000000000008</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="1">
+        <f>SUM(C2:C6)</f>
+        <v>1055.3100000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C9" s="4">
         <v>1400</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
-      <c r="B9" s="2" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="1">
-        <f>C8-C7</f>
-        <v>409.58999999999992</v>
+      <c r="C10" s="1">
+        <f>C9-C8</f>
+        <v>344.68999999999983</v>
       </c>
     </row>
   </sheetData>
